--- a/data/trans_orig/IP3104-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP3104-Estudios-trans_orig.xlsx
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>7030</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9286</t>
+          <t>8663</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14207</t>
+          <t>13545</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33148</t>
+          <t>32310</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48936</t>
+          <t>47191</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26958</t>
+          <t>27136</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>41053</t>
+          <t>40613</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>62200</t>
+          <t>63126</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>84049</t>
+          <t>83646</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,25%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17046</t>
+          <t>17727</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30430</t>
+          <t>31531</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22659</t>
+          <t>23210</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36458</t>
+          <t>36932</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44149</t>
+          <t>44691</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63669</t>
+          <t>62991</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>38,59%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10087</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21192</t>
+          <t>21123</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>4968</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14810</t>
+          <t>15638</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17772</t>
+          <t>18187</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32645</t>
+          <t>32914</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>678</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6454</t>
+          <t>6636</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7925</t>
+          <t>8445</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18030</t>
+          <t>18119</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33174</t>
+          <t>33905</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26602</t>
+          <t>26230</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45000</t>
+          <t>44257</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>49247</t>
+          <t>48266</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>74404</t>
+          <t>73179</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>205801</t>
+          <t>204760</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>235663</t>
+          <t>236890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,82 +1769,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>52,71%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>60,98%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>248260</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>230706</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>265019</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>55,38%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>51,46%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>59,11%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>469135</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>443359</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>492927</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>56,07%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>52,98%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>60,67%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>376</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>248260</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>230514</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>264876</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>55,38%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>51,42%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>59,08%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>469135</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>446399</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>492772</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>56,07%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>53,35%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>58,91%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>88844</t>
+          <t>89695</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>117203</t>
+          <t>118459</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>101822</t>
+          <t>102373</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>132711</t>
+          <t>131625</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>200052</t>
+          <t>197547</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>239919</t>
+          <t>239030</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23102</t>
+          <t>22974</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>40186</t>
+          <t>40095</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31298</t>
+          <t>30549</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>50519</t>
+          <t>51031</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>58643</t>
+          <t>58689</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>83527</t>
+          <t>85018</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4721</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13950</t>
+          <t>13812</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2108,82 +2108,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>9553</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>5486</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>15258</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
           <t>1,22%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>9553</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>5017</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>15185</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>17839</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>11731</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>24838</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>2,13%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>17839</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>11860</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>26046</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>13039</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11926</t>
+          <t>12689</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9411</t>
+          <t>8960</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22217</t>
+          <t>21291</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>77938</t>
+          <t>78367</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>97832</t>
+          <t>98073</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>73757</t>
+          <t>73013</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>91985</t>
+          <t>92389</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>155895</t>
+          <t>155177</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>182474</t>
+          <t>185252</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>61,74%</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36151</t>
+          <t>35892</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>54614</t>
+          <t>54675</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30559</t>
+          <t>30740</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>47618</t>
+          <t>48037</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>72386</t>
+          <t>72335</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>95689</t>
+          <t>98586</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>32,86%</t>
         </is>
       </c>
     </row>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9488</t>
+          <t>9424</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21578</t>
+          <t>21668</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>6841</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17702</t>
+          <t>17649</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19700</t>
+          <t>19619</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35603</t>
+          <t>35195</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>673</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>5377</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>8934</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>27176</t>
+          <t>27842</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>45939</t>
+          <t>46836</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>36920</t>
+          <t>36518</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>59119</t>
+          <t>57047</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>68825</t>
+          <t>68493</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>97022</t>
+          <t>97139</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>328696</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>367802</t>
+          <t>368966</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>343788</t>
+          <t>343961</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>384885</t>
+          <t>384556</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>684546</t>
+          <t>681866</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>741962</t>
+          <t>738788</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>56,83%</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>153156</t>
+          <t>155419</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>190480</t>
+          <t>192224</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>166625</t>
+          <t>166451</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>205170</t>
+          <t>203806</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>330172</t>
+          <t>332314</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>383238</t>
+          <t>382608</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,43%</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>50268</t>
+          <t>49516</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>74737</t>
+          <t>73136</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>49040</t>
+          <t>49438</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>73547</t>
+          <t>71980</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>105908</t>
+          <t>105354</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>141237</t>
+          <t>139220</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3655,12 +3655,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -3683,12 +3683,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7958</t>
+          <t>7371</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>19152</t>
+          <t>19058</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8687</t>
+          <t>8475</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>21355</t>
+          <t>20040</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,12 +3753,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>18992</t>
+          <t>19225</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>35698</t>
+          <t>35532</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2981</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11057</t>
+          <t>11170</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7639</t>
+          <t>7747</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18684</t>
+          <t>18141</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12905</t>
+          <t>12394</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26288</t>
+          <t>26904</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37204</t>
+          <t>37996</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51928</t>
+          <t>52743</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37122</t>
+          <t>38003</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>52087</t>
+          <t>52876</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>77531</t>
+          <t>79542</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>99693</t>
+          <t>101506</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>60,59%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16467</t>
+          <t>16948</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30182</t>
+          <t>29730</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13513</t>
+          <t>13507</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26311</t>
+          <t>26408</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33442</t>
+          <t>33329</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51487</t>
+          <t>51344</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,65%</t>
         </is>
       </c>
     </row>
@@ -4596,12 +4596,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5442</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14268</t>
+          <t>14530</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>600</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4814</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>6396</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18180</t>
+          <t>16950</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>716</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6833</t>
+          <t>6470</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>859</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7753</t>
+          <t>8293</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4759,12 +4759,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11339</t>
+          <t>11982</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12850</t>
+          <t>12556</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26741</t>
+          <t>26679</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18975</t>
+          <t>18897</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36808</t>
+          <t>35239</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>34339</t>
+          <t>35015</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>55455</t>
+          <t>56190</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -5165,12 +5165,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>190350</t>
+          <t>192130</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>223840</t>
+          <t>224508</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>208358</t>
+          <t>206275</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>243357</t>
+          <t>241307</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>408993</t>
+          <t>410561</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>458088</t>
+          <t>458134</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>53,98%</t>
         </is>
       </c>
     </row>
@@ -5278,12 +5278,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>107859</t>
+          <t>107045</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>137880</t>
+          <t>136665</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>122827</t>
+          <t>122690</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>155729</t>
+          <t>155684</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>239522</t>
+          <t>238480</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>285714</t>
+          <t>283091</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,36%</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32798</t>
+          <t>33386</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51993</t>
+          <t>52827</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31554</t>
+          <t>31399</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51889</t>
+          <t>51494</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>69117</t>
+          <t>69163</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>96023</t>
+          <t>97092</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,44%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10129</t>
+          <t>9657</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23292</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7564</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18784</t>
+          <t>18282</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20453</t>
+          <t>19989</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37439</t>
+          <t>37583</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -5847,12 +5847,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14247</t>
+          <t>13726</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>4653</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15641</t>
+          <t>15420</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11224</t>
+          <t>11747</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25326</t>
+          <t>25836</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -5960,12 +5960,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>65639</t>
+          <t>66440</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>85925</t>
+          <t>85842</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>64869</t>
+          <t>64735</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>85821</t>
+          <t>85515</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>136297</t>
+          <t>136195</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>166368</t>
+          <t>164819</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>54,7%</t>
         </is>
       </c>
     </row>
@@ -6073,12 +6073,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>42212</t>
+          <t>41926</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>61330</t>
+          <t>61079</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>40970</t>
+          <t>40672</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>59497</t>
+          <t>60098</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>89102</t>
+          <t>87233</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>116051</t>
+          <t>114384</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>37,96%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3519</t>
+          <t>3542</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12379</t>
+          <t>13221</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9347</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21391</t>
+          <t>21258</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15158</t>
+          <t>15217</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29604</t>
+          <t>30232</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12028</t>
+          <t>11898</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>7013</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5709</t>
+          <t>6074</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>16294</t>
+          <t>17459</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -6642,12 +6642,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>24501</t>
+          <t>24818</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>43159</t>
+          <t>42377</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6677,12 +6677,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>37384</t>
+          <t>37578</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>59557</t>
+          <t>60887</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>67151</t>
+          <t>67610</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>96254</t>
+          <t>94931</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>309157</t>
+          <t>305178</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>350016</t>
+          <t>351202</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6790,12 +6790,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>323199</t>
+          <t>323211</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>363850</t>
+          <t>366540</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6825,12 +6825,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>643911</t>
+          <t>641241</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>704013</t>
+          <t>703415</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,39%</t>
         </is>
       </c>
     </row>
@@ -6868,12 +6868,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>175899</t>
+          <t>176653</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>214555</t>
+          <t>215166</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>190687</t>
+          <t>188436</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>227841</t>
+          <t>228141</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>375884</t>
+          <t>377678</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>429567</t>
+          <t>431988</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,79%</t>
         </is>
       </c>
     </row>
@@ -6981,12 +6981,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>46824</t>
+          <t>47074</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>70271</t>
+          <t>70924</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>45461</t>
+          <t>46587</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>70030</t>
+          <t>70444</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>100064</t>
+          <t>97764</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>133299</t>
+          <t>131560</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -7094,12 +7094,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18082</t>
+          <t>18552</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>35391</t>
+          <t>35388</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -7129,12 +7129,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>12825</t>
+          <t>12765</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>27284</t>
+          <t>27096</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7164,12 +7164,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>34915</t>
+          <t>34771</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>56087</t>
+          <t>55184</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -7668,12 +7668,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>570</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5509</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7683,12 +7683,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7703,12 +7703,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7312</t>
+          <t>7835</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3143</t>
+          <t>3252</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>10798</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -7781,12 +7781,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7852</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17825</t>
+          <t>18022</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7796,12 +7796,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>7437</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17887</t>
+          <t>18095</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7851,12 +7851,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18428</t>
+          <t>18403</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32776</t>
+          <t>33363</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>27,03%</t>
         </is>
       </c>
     </row>
@@ -7894,12 +7894,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14584</t>
+          <t>14490</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26215</t>
+          <t>25814</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7909,12 +7909,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7929,12 +7929,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16985</t>
+          <t>17402</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30196</t>
+          <t>30639</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7964,12 +7964,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35289</t>
+          <t>34717</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53101</t>
+          <t>52140</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>42,24%</t>
         </is>
       </c>
     </row>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9549</t>
+          <t>10064</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20518</t>
+          <t>20520</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11247</t>
+          <t>10125</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22986</t>
+          <t>21732</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24001</t>
+          <t>23281</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39646</t>
+          <t>38536</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,22%</t>
         </is>
       </c>
     </row>
@@ -8120,12 +8120,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11256</t>
+          <t>11233</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8155,12 +8155,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17631</t>
+          <t>17747</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>12758</t>
+          <t>12570</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>25151</t>
+          <t>25402</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -8463,12 +8463,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9004</t>
+          <t>8849</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21068</t>
+          <t>20224</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8498,12 +8498,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>5510</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17359</t>
+          <t>16017</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>17304</t>
+          <t>17253</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>32663</t>
+          <t>33227</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -8576,12 +8576,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>143392</t>
+          <t>142783</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>177489</t>
+          <t>176834</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>149246</t>
+          <t>149158</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>183391</t>
+          <t>182407</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>302945</t>
+          <t>303496</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>350277</t>
+          <t>348230</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>38,92%</t>
         </is>
       </c>
     </row>
@@ -8689,12 +8689,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>136828</t>
+          <t>135971</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>169347</t>
+          <t>168308</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8704,12 +8704,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>149846</t>
+          <t>149820</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>184185</t>
+          <t>184214</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>294326</t>
+          <t>295954</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>341643</t>
+          <t>342747</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,3%</t>
         </is>
       </c>
     </row>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>61039</t>
+          <t>62083</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>85059</t>
+          <t>86468</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8817,12 +8817,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8837,12 +8837,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>60813</t>
+          <t>59872</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>85772</t>
+          <t>86278</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8852,12 +8852,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8872,12 +8872,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>128285</t>
+          <t>127877</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>163667</t>
+          <t>162721</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8887,12 +8887,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -8915,12 +8915,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29668</t>
+          <t>29907</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48900</t>
+          <t>48357</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8930,12 +8930,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8950,12 +8950,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33992</t>
+          <t>33485</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53797</t>
+          <t>54285</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8985,12 +8985,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69048</t>
+          <t>67120</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>96552</t>
+          <t>94137</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9000,12 +9000,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -9258,12 +9258,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12455</t>
+          <t>12540</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9273,12 +9273,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9293,12 +9293,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>2954</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12095</t>
+          <t>12164</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9328,12 +9328,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8564</t>
+          <t>8795</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20642</t>
+          <t>20450</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -9371,12 +9371,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>60182</t>
+          <t>59454</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>80104</t>
+          <t>79546</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9386,12 +9386,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9406,12 +9406,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62171</t>
+          <t>62732</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>83798</t>
+          <t>83909</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9421,12 +9421,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9441,12 +9441,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>125779</t>
+          <t>126412</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>157299</t>
+          <t>156038</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9456,12 +9456,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,05%</t>
         </is>
       </c>
     </row>
@@ -9484,12 +9484,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40869</t>
+          <t>41555</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>60108</t>
+          <t>60748</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9499,12 +9499,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9519,12 +9519,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>47641</t>
+          <t>47307</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>67662</t>
+          <t>67464</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9534,12 +9534,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9554,12 +9554,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>96065</t>
+          <t>94036</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>123080</t>
+          <t>122425</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9569,12 +9569,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,7%</t>
         </is>
       </c>
     </row>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18228</t>
+          <t>17491</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32991</t>
+          <t>32607</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9632,12 +9632,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14715</t>
+          <t>14456</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29006</t>
+          <t>28809</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9647,12 +9647,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>37134</t>
+          <t>36449</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>56373</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,36%</t>
         </is>
       </c>
     </row>
@@ -9710,12 +9710,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7581</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9725,12 +9725,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>5874</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16394</t>
+          <t>16730</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9760,12 +9760,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9780,12 +9780,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8661</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21042</t>
+          <t>21412</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -10053,12 +10053,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>16672</t>
+          <t>17592</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>32066</t>
+          <t>33066</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10088,12 +10088,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13864</t>
+          <t>14375</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>28521</t>
+          <t>30165</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10103,12 +10103,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>34006</t>
+          <t>34488</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>55396</t>
+          <t>54826</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -10166,12 +10166,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>222684</t>
+          <t>221998</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>262668</t>
+          <t>261939</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10181,12 +10181,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>228509</t>
+          <t>227770</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>272118</t>
+          <t>271195</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10216,12 +10216,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>465556</t>
+          <t>466295</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>524915</t>
+          <t>526996</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,24%</t>
         </is>
       </c>
     </row>
@@ -10279,12 +10279,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>202773</t>
+          <t>201642</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>242683</t>
+          <t>242869</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10294,12 +10294,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>226649</t>
+          <t>226001</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>269096</t>
+          <t>267799</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10329,12 +10329,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10349,12 +10349,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>439239</t>
+          <t>442072</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>498004</t>
+          <t>499370</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10364,12 +10364,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,18%</t>
         </is>
       </c>
     </row>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>97265</t>
+          <t>98586</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>128173</t>
+          <t>129892</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10427,12 +10427,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>94047</t>
+          <t>94350</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>125526</t>
+          <t>126515</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10442,12 +10442,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10462,12 +10462,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>200068</t>
+          <t>202340</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>244440</t>
+          <t>246259</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10477,12 +10477,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -10505,12 +10505,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>38858</t>
+          <t>38667</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>60833</t>
+          <t>60028</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10520,12 +10520,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10540,12 +10540,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>53336</t>
+          <t>53457</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>78418</t>
+          <t>79236</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10555,12 +10555,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10575,12 +10575,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>99564</t>
+          <t>99723</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>131815</t>
+          <t>130266</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10590,12 +10590,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -10971,7 +10971,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3093</t>
+          <t>3292</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11006,7 +11006,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5448</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11036,12 +11036,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>373</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5923</t>
+          <t>5379</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11051,12 +11051,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -11084,7 +11084,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>4943</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11119,7 +11119,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5765</t>
+          <t>6155</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11149,12 +11149,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>781</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7257</t>
+          <t>7140</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11164,12 +11164,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -11192,12 +11192,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15578</t>
+          <t>16020</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33850</t>
+          <t>33691</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11207,12 +11207,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11227,12 +11227,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13624</t>
+          <t>13742</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26358</t>
+          <t>27425</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11242,12 +11242,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11262,12 +11262,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32984</t>
+          <t>31857</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>56407</t>
+          <t>56600</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11277,12 +11277,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,52%</t>
         </is>
       </c>
     </row>
@@ -11305,12 +11305,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7094</t>
+          <t>6344</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21287</t>
+          <t>21774</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13218</t>
+          <t>13151</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26667</t>
+          <t>26404</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11355,12 +11355,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11375,12 +11375,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22411</t>
+          <t>22851</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43390</t>
+          <t>42725</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11390,12 +11390,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,13%</t>
         </is>
       </c>
     </row>
@@ -11418,12 +11418,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6784</t>
+          <t>6349</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19291</t>
+          <t>18460</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11453,12 +11453,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7832</t>
+          <t>8287</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19009</t>
+          <t>19492</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11468,12 +11468,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11488,12 +11488,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>16861</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34195</t>
+          <t>32905</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11503,12 +11503,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -11531,12 +11531,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9469</t>
+          <t>8684</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11566,12 +11566,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>8650</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11601,12 +11601,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4404</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14151</t>
+          <t>13638</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11616,12 +11616,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -11761,12 +11761,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4024</t>
+          <t>3643</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13339</t>
+          <t>13116</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11796,12 +11796,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12539</t>
+          <t>13455</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11811,12 +11811,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11831,12 +11831,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7675</t>
+          <t>7452</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21440</t>
+          <t>21363</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11846,12 +11846,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -11874,12 +11874,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12567</t>
+          <t>12698</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27539</t>
+          <t>27544</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11909,12 +11909,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13500</t>
+          <t>13769</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30042</t>
+          <t>30119</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11924,12 +11924,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11944,12 +11944,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30413</t>
+          <t>30001</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>52757</t>
+          <t>54454</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11959,12 +11959,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -11987,12 +11987,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>122618</t>
+          <t>118844</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>171071</t>
+          <t>168146</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12022,12 +12022,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>150700</t>
+          <t>149941</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>200335</t>
+          <t>204132</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12037,12 +12037,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>288034</t>
+          <t>288932</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>355383</t>
+          <t>358300</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12072,12 +12072,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,44%</t>
         </is>
       </c>
     </row>
@@ -12100,12 +12100,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108220</t>
+          <t>107536</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>152216</t>
+          <t>151731</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12115,12 +12115,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12135,12 +12135,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>146829</t>
+          <t>147231</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>189726</t>
+          <t>189980</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12150,12 +12150,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12170,12 +12170,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>266878</t>
+          <t>263559</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>330914</t>
+          <t>331247</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12185,12 +12185,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,61%</t>
         </is>
       </c>
     </row>
@@ -12213,12 +12213,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>95169</t>
+          <t>95108</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>183108</t>
+          <t>187019</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12228,12 +12228,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12248,12 +12248,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>104850</t>
+          <t>105683</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>144288</t>
+          <t>143470</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12263,12 +12263,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12283,12 +12283,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>212552</t>
+          <t>213805</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>309834</t>
+          <t>321923</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12298,12 +12298,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>33,64%</t>
         </is>
       </c>
     </row>
@@ -12326,12 +12326,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13846</t>
+          <t>13682</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28293</t>
+          <t>29203</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12341,12 +12341,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12361,12 +12361,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9304</t>
+          <t>9715</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22636</t>
+          <t>23722</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26062</t>
+          <t>25852</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46307</t>
+          <t>46479</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -12561,7 +12561,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12576,7 +12576,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12591,12 +12591,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>959</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9585</t>
+          <t>8632</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12606,12 +12606,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12626,12 +12626,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2181</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10769</t>
+          <t>11548</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12641,12 +12641,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -12669,12 +12669,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9512</t>
+          <t>9793</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12684,12 +12684,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12704,12 +12704,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3177</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13628</t>
+          <t>14132</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12719,12 +12719,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12739,12 +12739,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19436</t>
+          <t>19320</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12754,12 +12754,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -12782,12 +12782,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>45183</t>
+          <t>46246</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>65063</t>
+          <t>64945</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12797,12 +12797,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12817,12 +12817,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45978</t>
+          <t>45008</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>68805</t>
+          <t>68090</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12832,12 +12832,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12852,12 +12852,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>97558</t>
+          <t>98385</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>126725</t>
+          <t>128320</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12867,12 +12867,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>39,2%</t>
         </is>
       </c>
     </row>
@@ -12895,12 +12895,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52032</t>
+          <t>51944</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>71791</t>
+          <t>71927</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12910,12 +12910,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>76397</t>
+          <t>74937</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>99988</t>
+          <t>100468</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12945,12 +12945,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -12965,12 +12965,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>132430</t>
+          <t>132984</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>165394</t>
+          <t>164694</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12980,12 +12980,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>50,32%</t>
         </is>
       </c>
     </row>
@@ -13008,12 +13008,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10978</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23077</t>
+          <t>23206</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13023,12 +13023,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13043,12 +13043,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14388</t>
+          <t>14021</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28728</t>
+          <t>28632</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13078,12 +13078,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27704</t>
+          <t>28625</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>47152</t>
+          <t>47360</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -13121,12 +13121,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>2532</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12362</t>
+          <t>12600</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13136,12 +13136,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2524</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12348</t>
+          <t>12148</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13191,12 +13191,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6972</t>
+          <t>7114</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>19847</t>
+          <t>20394</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -13351,12 +13351,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16930</t>
+          <t>16551</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13386,12 +13386,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5097</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18011</t>
+          <t>18695</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13401,12 +13401,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13421,12 +13421,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13027</t>
+          <t>13140</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29013</t>
+          <t>28595</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13436,12 +13436,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -13464,12 +13464,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17177</t>
+          <t>17403</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>34850</t>
+          <t>34903</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13479,12 +13479,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13499,12 +13499,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20977</t>
+          <t>21379</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>40122</t>
+          <t>41972</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13514,12 +13514,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13534,12 +13534,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>42656</t>
+          <t>42183</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>67890</t>
+          <t>68308</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13549,12 +13549,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -13577,12 +13577,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>193207</t>
+          <t>192503</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>252312</t>
+          <t>252056</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13592,12 +13592,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -13612,12 +13612,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>222523</t>
+          <t>223734</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>280782</t>
+          <t>278655</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13627,12 +13627,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -13647,12 +13647,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>432302</t>
+          <t>439301</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>514859</t>
+          <t>523014</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13662,12 +13662,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>37,45%</t>
         </is>
       </c>
     </row>
@@ -13690,12 +13690,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>177677</t>
+          <t>178755</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>229615</t>
+          <t>233013</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13705,12 +13705,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13725,12 +13725,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>250983</t>
+          <t>250233</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>300081</t>
+          <t>301636</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13760,12 +13760,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>444852</t>
+          <t>444758</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>515741</t>
+          <t>518684</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,14%</t>
         </is>
       </c>
     </row>
@@ -13803,12 +13803,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>120618</t>
+          <t>121553</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>234528</t>
+          <t>224467</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13818,12 +13818,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>136564</t>
+          <t>136757</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>178280</t>
+          <t>180842</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13873,12 +13873,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>271963</t>
+          <t>272955</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>379125</t>
+          <t>375116</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,86%</t>
         </is>
       </c>
     </row>
@@ -13916,12 +13916,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22629</t>
+          <t>22723</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>40438</t>
+          <t>41493</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13931,12 +13931,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>17334</t>
+          <t>17931</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>35229</t>
+          <t>35567</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13986,12 +13986,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>44765</t>
+          <t>44503</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>70539</t>
+          <t>69296</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
